--- a/it_forms/017_cybersecurity_threat_mitigation_assessment_form--it_forms.xlsx
+++ b/it_forms/017_cybersecurity_threat_mitigation_assessment_form--it_forms.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -31,7 +32,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +43,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="004472C4"/>
         <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0070AD47"/>
+        <bgColor rgb="0070AD47"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,9 +64,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -427,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -510,15 +520,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>threat_mitigation_what</t>
+          <t>threat_mitigation_purpose</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>What</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What is the purpose of this threat assessment?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>(Optional) Describe the reason for this threat assessment</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -533,15 +547,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>threat_mitigation_what_2</t>
+          <t>threat_mitigation_goals</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>How</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>What are the primary goals for this threat assessment?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>(Optional) Describe the overall objectives of this threat assessment</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -551,20 +569,24 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>threat_mitigation_what_3</t>
+          <t>threat_mitigation_stakeholders</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>What</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>What are the key stakeholders involved in the threat assessment?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>(Optional) Identify key individuals or teams responsible for this threat assessment</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -579,15 +601,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>threat_mitigation_how</t>
+          <t>threat_mitigation_scope</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>How</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>What is the scope of the threat assessment?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>(Optional) Describe the scope of the threat assessment</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -602,15 +628,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>threat_mitigation_why</t>
+          <t>threat_mitigation_objectives</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Why</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>What are the threat assessment objectives?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>(Optional) Describe the specific objectives of the threat assessment</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -625,15 +655,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>threat_mitigation_what_6</t>
+          <t>threat_mitigation_identified_risks</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>What</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>What are the potential risks identified during the threat assessment?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>(Optional) Describe any identified risks or threats</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -648,15 +682,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>threat_mitigation_how_2</t>
+          <t>threat_mitigation_mitigation_strategies</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>How</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>What are the risk mitigation strategies implemented?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>(Optional) Describe the strategies to mitigate identified risks</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -671,15 +709,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>threat_mitigation_what_7</t>
+          <t>threat_mitigation_kpis</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>What</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>What are the key performance indicators (KPIs) for the threat assessment?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>(Optional) Describe the metrics used to measure the effectiveness of the threat assessment</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -694,15 +736,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>threat_mitigation_why_2</t>
+          <t>threat_mitigation_next_steps</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Why</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>What are the next steps in the threat assessment process?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>(Optional) Describe the next steps for the threat assessment process</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -717,15 +763,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>threat_mitigation_what_9</t>
+          <t>threat_mitigation_open_issues</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>What</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Are there any open issues or concerns?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>(Optional) Describe any open issues or concerns</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -740,15 +790,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>threat_mitigation_what_10</t>
+          <t>threat_mitigation_incident_response</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>What</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Is there an incident response plan in place?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>(Optional) Describe the incident response plan</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -763,15 +817,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>threat_mitigation_how_3</t>
+          <t>threat_mitigation_threat_assessment_report</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>How</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Is a threat assessment report available?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>(Optional) Describe the availability of the threat assessment report</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
@@ -781,20 +839,24 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>threat_mitigation_how_4</t>
+          <t>threat_mitigation_comments</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>How</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Are there any additional comments or recommendations?</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>(Optional) Provide any additional comments or recommendations</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
@@ -809,15 +871,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>threat_mitigation_what_8</t>
+          <t>threat_mitigation_technical_vulnerabilities</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>What</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Are there any technical vulnerabilities identified?</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>(Optional) Describe any technical vulnerabilities identified</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>no</t>
@@ -832,15 +898,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>threat_mitigation_why_3</t>
+          <t>threat_mitigation_physical_environmental_vulnerabilities</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Why</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Are there any physical or environmental vulnerabilities identified?</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>(Optional) Describe any physical or environmental vulnerabilities identified</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
@@ -855,15 +925,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>threat_mitigation_what_4</t>
+          <t>threat_mitigation_administrative_management_vulnerabilities</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>What</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Are there any administrative or management vulnerabilities identified?</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>(Optional) Describe any administrative or management vulnerabilities identified</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
@@ -878,15 +952,19 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>threat_mitigation_what_5</t>
+          <t>threat_mitigation_other_risks</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>What</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Are there any other risks or threats identified?</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>(Optional) Describe any other risks or threats identified</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>no</t>
@@ -901,177 +979,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>threat_mitigation_why_4</t>
+          <t>threat_mitigation_mitigation_plan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Why</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Is there a plan to address any identified risks or threats?</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>(Optional) Describe the plan to address identified risks or threats</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>threat_mitigation_why_5</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Why</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>threat_mitigation_what_11</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>What</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>threat_mitigation_what_12</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>What</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>threat_mitigation_why_6</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Why</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>threat_mitigation_how_6</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>How</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>threat_mitigation_what_14</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>What</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>threat_mitigation_why_7</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Why</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1083,6 +1004,127 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>list_name</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>threat_mitigation_stakeholders_choices</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>it_manager</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>IT Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>threat_mitigation_stakeholders_choices</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>security_team</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Security Team</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>threat_mitigation_stakeholders_choices</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>management_team</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Management Team</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>threat_mitigation_stakeholders_choices</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>risk_management_team</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Risk Management Team</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>threat_mitigation_stakeholders_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>other_(specify)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Other (specify)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
